--- a/output/98,3,0/info.xlsx
+++ b/output/98,3,0/info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,31 +485,31 @@
         <v>0.008</v>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>60.20435414479233</v>
+        <v>54.17376373647539</v>
       </c>
       <c r="D2" t="n">
-        <v>65.80109179859015</v>
+        <v>98.02626436927231</v>
       </c>
       <c r="E2" t="n">
-        <v>92.31396429974184</v>
+        <v>72.95390115024789</v>
       </c>
       <c r="F2" t="n">
-        <v>3.394797888550282</v>
+        <v>2.93252160241905</v>
       </c>
       <c r="G2" t="n">
-        <v>230.5022565844611</v>
+        <v>296.4232476911237</v>
       </c>
       <c r="H2" t="n">
-        <v>177.6459918382634</v>
+        <v>228.4349143872575</v>
       </c>
       <c r="I2" t="n">
         <v>355</v>
       </c>
       <c r="J2" t="n">
-        <v>363.9190589696775</v>
+        <v>547.7240174101286</v>
       </c>
     </row>
     <row r="3">
@@ -517,31 +517,31 @@
         <v>0.008</v>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>61.18207875669168</v>
+        <v>55.20005144894402</v>
       </c>
       <c r="D3" t="n">
-        <v>63.25564589832344</v>
+        <v>95.70847912487217</v>
       </c>
       <c r="E3" t="n">
-        <v>93.05688366898073</v>
+        <v>72.92671300801115</v>
       </c>
       <c r="F3" t="n">
-        <v>3.402900320258226</v>
+        <v>2.953442445546706</v>
       </c>
       <c r="G3" t="n">
-        <v>230.5022565844611</v>
+        <v>296.4232476911237</v>
       </c>
       <c r="H3" t="n">
-        <v>177.6459918382634</v>
+        <v>228.4349143872575</v>
       </c>
       <c r="I3" t="n">
         <v>355</v>
       </c>
       <c r="J3" t="n">
-        <v>363.9190589696775</v>
+        <v>547.7240174101286</v>
       </c>
     </row>
     <row r="4">
@@ -549,31 +549,31 @@
         <v>0.008</v>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>62.1542021957592</v>
+        <v>56.21792969509094</v>
       </c>
       <c r="D4" t="n">
-        <v>60.68528192512217</v>
+        <v>93.34092073005662</v>
       </c>
       <c r="E4" t="n">
-        <v>93.87324123103237</v>
+        <v>72.89787107344625</v>
       </c>
       <c r="F4" t="n">
-        <v>3.409514651862507</v>
+        <v>2.974113082360172</v>
       </c>
       <c r="G4" t="n">
-        <v>230.5022565844611</v>
+        <v>296.4232476911237</v>
       </c>
       <c r="H4" t="n">
-        <v>177.6459918382634</v>
+        <v>228.4349143872575</v>
       </c>
       <c r="I4" t="n">
         <v>355</v>
       </c>
       <c r="J4" t="n">
-        <v>363.9190589696775</v>
+        <v>547.7240174101286</v>
       </c>
     </row>
     <row r="5">
@@ -581,31 +581,31 @@
         <v>0.008</v>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>63.12215887128328</v>
+        <v>57.22711716555131</v>
       </c>
       <c r="D5" t="n">
-        <v>58.09239620133304</v>
+        <v>90.92897843374458</v>
       </c>
       <c r="E5" t="n">
-        <v>94.77340889638734</v>
+        <v>72.86756587141359</v>
       </c>
       <c r="F5" t="n">
-        <v>3.414505901889987</v>
+        <v>2.994297199590662</v>
       </c>
       <c r="G5" t="n">
-        <v>230.5022565844611</v>
+        <v>296.4232476911237</v>
       </c>
       <c r="H5" t="n">
-        <v>177.6459918382634</v>
+        <v>228.4349143872575</v>
       </c>
       <c r="I5" t="n">
         <v>355</v>
       </c>
       <c r="J5" t="n">
-        <v>363.9190589696775</v>
+        <v>547.7240174101286</v>
       </c>
     </row>
     <row r="6">
@@ -613,31 +613,31 @@
         <v>0.008</v>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
-        <v>64.08761848322851</v>
+        <v>58.22764453794507</v>
       </c>
       <c r="D6" t="n">
-        <v>55.4789411208449</v>
+        <v>88.47756605743409</v>
       </c>
       <c r="E6" t="n">
-        <v>95.76992601130877</v>
+        <v>72.83599662778953</v>
       </c>
       <c r="F6" t="n">
-        <v>3.41774732325615</v>
+        <v>3.013776824948379</v>
       </c>
       <c r="G6" t="n">
-        <v>230.5022565844611</v>
+        <v>296.4232476911237</v>
       </c>
       <c r="H6" t="n">
-        <v>177.6459918382634</v>
+        <v>228.4349143872575</v>
       </c>
       <c r="I6" t="n">
         <v>355</v>
       </c>
       <c r="J6" t="n">
-        <v>363.9190589696775</v>
+        <v>547.7240174101286</v>
       </c>
     </row>
     <row r="7">
@@ -645,31 +645,31 @@
         <v>0.008</v>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>65.05246662746862</v>
+        <v>59.2198469317912</v>
       </c>
       <c r="D7" t="n">
-        <v>52.84647027680678</v>
+        <v>85.99109410477502</v>
       </c>
       <c r="E7" t="n">
-        <v>96.87807349667169</v>
+        <v>72.80337386328624</v>
       </c>
       <c r="F7" t="n">
-        <v>3.419118368997445</v>
+        <v>3.032351885343413</v>
       </c>
       <c r="G7" t="n">
-        <v>230.5022565844611</v>
+        <v>296.4232476911237</v>
       </c>
       <c r="H7" t="n">
-        <v>177.6459918382634</v>
+        <v>228.4349143872575</v>
       </c>
       <c r="I7" t="n">
         <v>355</v>
       </c>
       <c r="J7" t="n">
-        <v>363.9190589696775</v>
+        <v>547.7240174101286</v>
       </c>
     </row>
     <row r="8">
@@ -677,31 +677,31 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>60.20435414479233</v>
+        <v>52.09867422049707</v>
       </c>
       <c r="D8" t="n">
-        <v>61.27506819986218</v>
+        <v>97.96283499957947</v>
       </c>
       <c r="E8" t="n">
-        <v>93.86889639478738</v>
+        <v>73.08297727518929</v>
       </c>
       <c r="F8" t="n">
-        <v>3.405296150455272</v>
+        <v>2.931496440246959</v>
       </c>
       <c r="G8" t="n">
-        <v>194.1775409571732</v>
+        <v>258.3224011457655</v>
       </c>
       <c r="H8" t="n">
-        <v>149.6537676854777</v>
+        <v>199.082734944326</v>
       </c>
       <c r="I8" t="n">
         <v>355</v>
       </c>
       <c r="J8" t="n">
-        <v>302.2223679026242</v>
+        <v>474.9991963237957</v>
       </c>
     </row>
     <row r="9">
@@ -709,31 +709,31 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>61.18207875669168</v>
+        <v>53.13966510367932</v>
       </c>
       <c r="D9" t="n">
-        <v>58.72961810517035</v>
+        <v>95.76244289543237</v>
       </c>
       <c r="E9" t="n">
-        <v>94.73646217837913</v>
+        <v>73.06038563952767</v>
       </c>
       <c r="F9" t="n">
-        <v>3.411316773620924</v>
+        <v>2.950332247424431</v>
       </c>
       <c r="G9" t="n">
-        <v>194.1775409571732</v>
+        <v>258.3224011457655</v>
       </c>
       <c r="H9" t="n">
-        <v>149.6537676854777</v>
+        <v>199.082734944326</v>
       </c>
       <c r="I9" t="n">
         <v>355</v>
       </c>
       <c r="J9" t="n">
-        <v>302.2223679026242</v>
+        <v>474.9991963237957</v>
       </c>
     </row>
     <row r="10">
@@ -741,31 +741,31 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>62.1542021957592</v>
+        <v>54.17376373647539</v>
       </c>
       <c r="D10" t="n">
-        <v>56.15925266640881</v>
+        <v>93.50025932268974</v>
       </c>
       <c r="E10" t="n">
-        <v>95.69548442322773</v>
+        <v>73.03577068731083</v>
       </c>
       <c r="F10" t="n">
-        <v>3.415828597554383</v>
+        <v>2.969393882513538</v>
       </c>
       <c r="G10" t="n">
-        <v>194.1775409571732</v>
+        <v>258.3224011457655</v>
       </c>
       <c r="H10" t="n">
-        <v>149.6537676854777</v>
+        <v>199.082734944326</v>
       </c>
       <c r="I10" t="n">
         <v>355</v>
       </c>
       <c r="J10" t="n">
-        <v>302.2223679026242</v>
+        <v>474.9991963237957</v>
       </c>
     </row>
     <row r="11">
@@ -773,31 +773,31 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>63.12215887128328</v>
+        <v>55.20005144894402</v>
       </c>
       <c r="D11" t="n">
-        <v>53.56636828431651</v>
+        <v>91.18247992059045</v>
       </c>
       <c r="E11" t="n">
-        <v>96.75991560371234</v>
+        <v>73.00931406915154</v>
       </c>
       <c r="F11" t="n">
-        <v>3.41869862662408</v>
+        <v>2.988414824272656</v>
       </c>
       <c r="G11" t="n">
-        <v>194.1775409571732</v>
+        <v>258.3224011457655</v>
       </c>
       <c r="H11" t="n">
-        <v>149.6537676854777</v>
+        <v>199.082734944326</v>
       </c>
       <c r="I11" t="n">
         <v>355</v>
       </c>
       <c r="J11" t="n">
-        <v>302.2223679026242</v>
+        <v>474.9991963237957</v>
       </c>
     </row>
     <row r="12">
@@ -805,31 +805,31 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C12" t="n">
-        <v>64.08761848322851</v>
+        <v>56.21792969509094</v>
       </c>
       <c r="D12" t="n">
-        <v>50.95291742236026</v>
+        <v>88.8149263041729</v>
       </c>
       <c r="E12" t="n">
-        <v>97.94684086786668</v>
+        <v>72.98120426622438</v>
       </c>
       <c r="F12" t="n">
-        <v>3.419801739167198</v>
+        <v>3.007145404151339</v>
       </c>
       <c r="G12" t="n">
-        <v>194.1775409571732</v>
+        <v>258.3224011457655</v>
       </c>
       <c r="H12" t="n">
-        <v>149.6537676854777</v>
+        <v>199.082734944326</v>
       </c>
       <c r="I12" t="n">
         <v>355</v>
       </c>
       <c r="J12" t="n">
-        <v>302.2223679026242</v>
+        <v>474.9991963237957</v>
       </c>
     </row>
     <row r="13">
@@ -837,223 +837,95 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C13" t="n">
-        <v>65.05246662746862</v>
+        <v>57.22711716555131</v>
       </c>
       <c r="D13" t="n">
-        <v>48.32045361659877</v>
+        <v>86.40298763982254</v>
       </c>
       <c r="E13" t="n">
-        <v>99.27738087751561</v>
+        <v>72.9516378549244</v>
       </c>
       <c r="F13" t="n">
-        <v>3.419018689706309</v>
+        <v>3.025353719595409</v>
       </c>
       <c r="G13" t="n">
-        <v>194.1775409571732</v>
+        <v>258.3224011457655</v>
       </c>
       <c r="H13" t="n">
-        <v>149.6537676854777</v>
+        <v>199.082734944326</v>
       </c>
       <c r="I13" t="n">
         <v>355</v>
       </c>
       <c r="J13" t="n">
-        <v>302.2223679026242</v>
+        <v>474.9991963237957</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="B14" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" t="n">
-        <v>60.20435414479233</v>
+        <v>58.22764453794507</v>
       </c>
       <c r="D14" t="n">
-        <v>56.74903903136889</v>
+        <v>83.95157767662128</v>
       </c>
       <c r="E14" t="n">
-        <v>95.6718548053932</v>
+        <v>72.92082158255322</v>
       </c>
       <c r="F14" t="n">
-        <v>3.41209255646431</v>
+        <v>3.042825809886176</v>
       </c>
       <c r="G14" t="n">
-        <v>165.1182610422484</v>
+        <v>258.3224011457655</v>
       </c>
       <c r="H14" t="n">
-        <v>127.2602686829878</v>
+        <v>199.082734944326</v>
       </c>
       <c r="I14" t="n">
         <v>355</v>
       </c>
       <c r="J14" t="n">
-        <v>252.866440882635</v>
+        <v>474.9991963237957</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="B15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15" t="n">
-        <v>61.18207875669168</v>
+        <v>59.2198469317912</v>
       </c>
       <c r="D15" t="n">
-        <v>54.20358959591344</v>
+        <v>81.4651068551406</v>
       </c>
       <c r="E15" t="n">
-        <v>96.69653043788354</v>
+        <v>72.88897540591667</v>
       </c>
       <c r="F15" t="n">
-        <v>3.416030830152386</v>
+        <v>3.059365192629344</v>
       </c>
       <c r="G15" t="n">
-        <v>165.1182610422484</v>
+        <v>258.3224011457655</v>
       </c>
       <c r="H15" t="n">
-        <v>127.2602686829878</v>
+        <v>199.082734944326</v>
       </c>
       <c r="I15" t="n">
         <v>355</v>
       </c>
       <c r="J15" t="n">
-        <v>252.866440882635</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="B16" t="n">
-        <v>62</v>
-      </c>
-      <c r="C16" t="n">
-        <v>62.1542021957592</v>
-      </c>
-      <c r="D16" t="n">
-        <v>51.63322759276125</v>
-      </c>
-      <c r="E16" t="n">
-        <v>97.83719144669122</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3.418439662290489</v>
-      </c>
-      <c r="G16" t="n">
-        <v>165.1182610422484</v>
-      </c>
-      <c r="H16" t="n">
-        <v>127.2602686829878</v>
-      </c>
-      <c r="I16" t="n">
-        <v>355</v>
-      </c>
-      <c r="J16" t="n">
-        <v>252.866440882635</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="B17" t="n">
-        <v>63</v>
-      </c>
-      <c r="C17" t="n">
-        <v>63.12215887128328</v>
-      </c>
-      <c r="D17" t="n">
-        <v>49.04034947385296</v>
-      </c>
-      <c r="E17" t="n">
-        <v>99.11309708743244</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3.419188045269328</v>
-      </c>
-      <c r="G17" t="n">
-        <v>165.1182610422484</v>
-      </c>
-      <c r="H17" t="n">
-        <v>127.2602686829878</v>
-      </c>
-      <c r="I17" t="n">
-        <v>355</v>
-      </c>
-      <c r="J17" t="n">
-        <v>252.866440882635</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="B18" t="n">
-        <v>64</v>
-      </c>
-      <c r="C18" t="n">
-        <v>64.08761848322851</v>
-      </c>
-      <c r="D18" t="n">
-        <v>46.42690669042714</v>
-      </c>
-      <c r="E18" t="n">
-        <v>100.548195630908</v>
-      </c>
-      <c r="F18" t="n">
-        <v>3.418152484752497</v>
-      </c>
-      <c r="G18" t="n">
-        <v>165.1182610422484</v>
-      </c>
-      <c r="H18" t="n">
-        <v>127.2602686829878</v>
-      </c>
-      <c r="I18" t="n">
-        <v>355</v>
-      </c>
-      <c r="J18" t="n">
-        <v>252.866440882635</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="B19" t="n">
-        <v>65</v>
-      </c>
-      <c r="C19" t="n">
-        <v>65.05246662746862</v>
-      </c>
-      <c r="D19" t="n">
-        <v>43.7944503429609</v>
-      </c>
-      <c r="E19" t="n">
-        <v>102.1726079106213</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3.415215038431888</v>
-      </c>
-      <c r="G19" t="n">
-        <v>165.1182610422484</v>
-      </c>
-      <c r="H19" t="n">
-        <v>127.2602686829878</v>
-      </c>
-      <c r="I19" t="n">
-        <v>355</v>
-      </c>
-      <c r="J19" t="n">
-        <v>252.866440882635</v>
+        <v>474.9991963237957</v>
       </c>
     </row>
   </sheetData>
